--- a/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0001T0006Z000C1N69_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0001T0006Z000C1N69_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>24.41272073808578</v>
+        <v>3.967067119938939</v>
       </c>
       <c r="D2" t="n">
-        <v>22.01593450090276</v>
+        <v>3.577589356396699</v>
       </c>
       <c r="E2" t="n">
-        <v>11.85638557684227</v>
+        <v>1.926662656236869</v>
       </c>
       <c r="F2" t="n">
-        <v>4.365984819843646</v>
+        <v>0.7094725332245927</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>47.80251029847862</v>
+        <v>7.767907923502777</v>
       </c>
       <c r="D3" t="n">
-        <v>24.48103937872124</v>
+        <v>3.978168899042201</v>
       </c>
       <c r="E3" t="n">
-        <v>11.85638557684227</v>
+        <v>1.926662656236869</v>
       </c>
       <c r="F3" t="n">
-        <v>4.365984819843646</v>
+        <v>0.7094725332245927</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>26.34764953113272</v>
+        <v>4.281493048809066</v>
       </c>
       <c r="D4" t="n">
-        <v>29.55885295360685</v>
+        <v>4.803313604961113</v>
       </c>
       <c r="E4" t="n">
-        <v>11.85638557684227</v>
+        <v>1.926662656236869</v>
       </c>
       <c r="F4" t="n">
-        <v>4.365984819843646</v>
+        <v>0.7094725332245927</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>15.52417469626002</v>
+        <v>2.522678388142254</v>
       </c>
       <c r="D5" t="n">
-        <v>17.46424919657298</v>
+        <v>2.837940494443109</v>
       </c>
       <c r="E5" t="n">
-        <v>11.85638557684227</v>
+        <v>1.926662656236869</v>
       </c>
       <c r="F5" t="n">
-        <v>4.365984819843646</v>
+        <v>0.7094725332245927</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
